--- a/test-data/RD_Jachymov_dum/outputs/Vykaz_vymer_RD_Jachymov_VSE_VARIANTY_2026-05-29.xlsx
+++ b/test-data/RD_Jachymov_dum/outputs/Vykaz_vymer_RD_Jachymov_VSE_VARIANTY_2026-05-29.xlsx
@@ -97,11 +97,11 @@
       <color rgb="00A04000"/>
     </font>
     <font>
-      <b val="1"/>
+      <i val="1"/>
       <color rgb="009C0006"/>
     </font>
     <font>
-      <i val="1"/>
+      <b val="1"/>
       <color rgb="009C0006"/>
     </font>
     <font>
@@ -310,10 +310,10 @@
     <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -1085,7 +1085,7 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>8 WebSearch verified (3.7 %) ✓ | 9 wrong leaf flagged (4.2 %) ⚠ | 142 needs_production_lookup (66.4 %)</t>
+          <t>8 WebSearch verified (3.7 %) ✓ | 5 wrong leaf flagged (2.3 %) ⚠ | 142 needs_production_lookup (66.4 %)</t>
         </is>
       </c>
     </row>
@@ -2186,7 +2186,7 @@
       </c>
       <c r="J5" s="8" t="inlineStr">
         <is>
-          <t>URS-prop 564831111</t>
+          <t>URS-prop 596811220</t>
         </is>
       </c>
     </row>
@@ -2226,7 +2226,7 @@
       </c>
       <c r="J6" s="8" t="inlineStr">
         <is>
-          <t>URS-prop 564831111</t>
+          <t>URS-prop 636311??? ?</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="J18" s="8" t="inlineStr">
         <is>
-          <t>URS-prop 631311115</t>
+          <t>URS-prop 274??? ?</t>
         </is>
       </c>
     </row>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="J23" s="8" t="inlineStr">
         <is>
-          <t>URS-prop 631311115</t>
+          <t>URS-prop 274??? ?</t>
         </is>
       </c>
     </row>
@@ -6984,7 +6984,7 @@
       </c>
       <c r="D5" s="20" t="inlineStr">
         <is>
-          <t>564831111</t>
+          <t>596811220</t>
         </is>
       </c>
       <c r="E5" s="8" t="inlineStr">
@@ -7012,7 +7012,7 @@
       </c>
       <c r="L5" s="20" t="inlineStr">
         <is>
-          <t>wrong_leaf_disambiguation_needed</t>
+          <t>family_verified_leaf_candidate_verify_stage3</t>
         </is>
       </c>
       <c r="M5" s="8" t="inlineStr">
@@ -7025,9 +7025,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="O5" s="27" t="inlineStr">
-        <is>
-          <t>LEAF CHYBNÝ — viz alternatives</t>
+      <c r="O5" s="26" t="inlineStr">
+        <is>
+          <t>ANO</t>
         </is>
       </c>
     </row>
@@ -7045,9 +7045,9 @@
           <t>Terasa garapa — podkladní rošt</t>
         </is>
       </c>
-      <c r="D6" s="20" t="inlineStr">
-        <is>
-          <t>564831111</t>
+      <c r="D6" s="27" t="inlineStr">
+        <is>
+          <t>636311??? ?</t>
         </is>
       </c>
       <c r="E6" s="8" t="inlineStr">
@@ -7075,7 +7075,7 @@
       </c>
       <c r="L6" s="20" t="inlineStr">
         <is>
-          <t>wrong_leaf_disambiguation_needed</t>
+          <t>family_636311_leaf_lookup_required</t>
         </is>
       </c>
       <c r="M6" s="8" t="inlineStr">
@@ -7088,9 +7088,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="O6" s="27" t="inlineStr">
-        <is>
-          <t>LEAF CHYBNÝ — viz alternatives</t>
+      <c r="O6" s="26" t="inlineStr">
+        <is>
+          <t>ANO</t>
         </is>
       </c>
     </row>
@@ -7171,7 +7171,7 @@
           <t>Odvoz výkopu</t>
         </is>
       </c>
-      <c r="D8" s="28" t="inlineStr">
+      <c r="D8" s="27" t="inlineStr">
         <is>
           <t>162701??? ?</t>
         </is>
@@ -7485,9 +7485,9 @@
           <t>Bílá vana — bednění systémové</t>
         </is>
       </c>
-      <c r="D13" s="20" t="inlineStr">
-        <is>
-          <t>631311115</t>
+      <c r="D13" s="27" t="inlineStr">
+        <is>
+          <t>274??? ?</t>
         </is>
       </c>
       <c r="E13" s="8" t="inlineStr">
@@ -7515,7 +7515,7 @@
       </c>
       <c r="L13" s="20" t="inlineStr">
         <is>
-          <t>wrong_leaf_disambiguation_needed</t>
+          <t>wrong_leaf_274_family_lookup_required</t>
         </is>
       </c>
       <c r="M13" s="8" t="inlineStr">
@@ -7528,9 +7528,9 @@
           <t>#3</t>
         </is>
       </c>
-      <c r="O13" s="27" t="inlineStr">
-        <is>
-          <t>LEAF CHYBNÝ — viz alternatives</t>
+      <c r="O13" s="26" t="inlineStr">
+        <is>
+          <t>ANO</t>
         </is>
       </c>
     </row>
@@ -7611,7 +7611,7 @@
           <t>Bílá vana — separační fólie</t>
         </is>
       </c>
-      <c r="D15" s="28" t="inlineStr">
+      <c r="D15" s="27" t="inlineStr">
         <is>
           <t>711141??? ?</t>
         </is>
@@ -7654,7 +7654,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="O15" s="27" t="inlineStr">
+      <c r="O15" s="28" t="inlineStr">
         <is>
           <t>LEAF CHYBNÝ — viz alternatives</t>
         </is>
@@ -7800,9 +7800,9 @@
           <t>Pozední věnec — bednění</t>
         </is>
       </c>
-      <c r="D18" s="20" t="inlineStr">
-        <is>
-          <t>631311115</t>
+      <c r="D18" s="27" t="inlineStr">
+        <is>
+          <t>274??? ?</t>
         </is>
       </c>
       <c r="E18" s="8" t="inlineStr">
@@ -7830,7 +7830,7 @@
       </c>
       <c r="L18" s="20" t="inlineStr">
         <is>
-          <t>wrong_leaf_disambiguation_needed</t>
+          <t>wrong_leaf_274_family_lookup_required</t>
         </is>
       </c>
       <c r="M18" s="8" t="inlineStr">
@@ -7843,9 +7843,9 @@
           <t>#3</t>
         </is>
       </c>
-      <c r="O18" s="27" t="inlineStr">
-        <is>
-          <t>LEAF CHYBNÝ — viz alternatives</t>
+      <c r="O18" s="26" t="inlineStr">
+        <is>
+          <t>ANO</t>
         </is>
       </c>
     </row>
@@ -10572,7 +10572,7 @@
           <t>Bourání plechové střešní krytiny</t>
         </is>
       </c>
-      <c r="D62" s="28" t="inlineStr">
+      <c r="D62" s="27" t="inlineStr">
         <is>
           <t>762??? ?</t>
         </is>
@@ -10615,7 +10615,7 @@
           <t>#9</t>
         </is>
       </c>
-      <c r="O62" s="27" t="inlineStr">
+      <c r="O62" s="28" t="inlineStr">
         <is>
           <t>LEAF CHYBNÝ — viz alternatives</t>
         </is>
@@ -12084,7 +12084,7 @@
           <t>HI koupelny 1.NP + 2.NP + 3.NP</t>
         </is>
       </c>
-      <c r="D86" s="28" t="inlineStr">
+      <c r="D86" s="27" t="inlineStr">
         <is>
           <t>711??? ?</t>
         </is>
@@ -12147,7 +12147,7 @@
           <t>Podlahový EPS 150</t>
         </is>
       </c>
-      <c r="D87" s="28" t="inlineStr">
+      <c r="D87" s="27" t="inlineStr">
         <is>
           <t>713121??? ?</t>
         </is>
@@ -12210,7 +12210,7 @@
           <t>Kročejová EPS nad ocelobeton</t>
         </is>
       </c>
-      <c r="D88" s="28" t="inlineStr">
+      <c r="D88" s="27" t="inlineStr">
         <is>
           <t>713121??? ?</t>
         </is>
@@ -18942,7 +18942,7 @@
           <t>Odvoz výkopu sklad</t>
         </is>
       </c>
-      <c r="D7" s="28" t="inlineStr">
+      <c r="D7" s="27" t="inlineStr">
         <is>
           <t>162701??? ?</t>
         </is>
@@ -18984,7 +18984,7 @@
           <t>#10</t>
         </is>
       </c>
-      <c r="O7" s="27" t="inlineStr">
+      <c r="O7" s="28" t="inlineStr">
         <is>
           <t>LEAF CHYBNÝ — viz alternatives</t>
         </is>
@@ -19004,7 +19004,7 @@
           <t>Základové pasy sklad</t>
         </is>
       </c>
-      <c r="D8" s="28" t="inlineStr">
+      <c r="D8" s="27" t="inlineStr">
         <is>
           <t>271313??? ?</t>
         </is>
@@ -19047,7 +19047,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="O8" s="27" t="inlineStr">
+      <c r="O8" s="28" t="inlineStr">
         <is>
           <t>LEAF CHYBNÝ — viz alternatives</t>
         </is>
@@ -20075,7 +20075,7 @@
           <t>Betonová dlažba sklad</t>
         </is>
       </c>
-      <c r="D25" s="28" t="inlineStr">
+      <c r="D25" s="27" t="inlineStr">
         <is>
           <t>596??? ?</t>
         </is>
@@ -20118,7 +20118,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="O25" s="27" t="inlineStr">
+      <c r="O25" s="28" t="inlineStr">
         <is>
           <t>LEAF CHYBNÝ — viz alternatives</t>
         </is>
@@ -22434,7 +22434,7 @@
           <t>162701105</t>
         </is>
       </c>
-      <c r="B4" s="27" t="inlineStr">
+      <c r="B4" s="28" t="inlineStr">
         <is>
           <t>⚠ wrong_leaf (distance)</t>
         </is>
@@ -22476,7 +22476,7 @@
           <t>711132101</t>
         </is>
       </c>
-      <c r="B5" s="27" t="inlineStr">
+      <c r="B5" s="28" t="inlineStr">
         <is>
           <t>⚠ wrong_leaf (material)</t>
         </is>
@@ -22518,7 +22518,7 @@
           <t>962081141</t>
         </is>
       </c>
-      <c r="B6" s="27" t="inlineStr">
+      <c r="B6" s="28" t="inlineStr">
         <is>
           <t>❌ wrong_work_type</t>
         </is>
@@ -22560,7 +22560,7 @@
           <t>771121011</t>
         </is>
       </c>
-      <c r="B7" s="27" t="inlineStr">
+      <c r="B7" s="28" t="inlineStr">
         <is>
           <t>❌ wrong_work_type</t>
         </is>
@@ -22770,7 +22770,7 @@
           <t>713141121</t>
         </is>
       </c>
-      <c r="B12" s="27" t="inlineStr">
+      <c r="B12" s="28" t="inlineStr">
         <is>
           <t>❌ wrong_location</t>
         </is>
@@ -22812,7 +22812,7 @@
           <t>273313811</t>
         </is>
       </c>
-      <c r="B13" s="27" t="inlineStr">
+      <c r="B13" s="28" t="inlineStr">
         <is>
           <t>❌ wrong_geometry</t>
         </is>

--- a/test-data/RD_Jachymov_dum/outputs/Vykaz_vymer_RD_Jachymov_VSE_VARIANTY_2026-05-29.xlsx
+++ b/test-data/RD_Jachymov_dum/outputs/Vykaz_vymer_RD_Jachymov_VSE_VARIANTY_2026-05-29.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Souhrn" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Var_A_Agregovany_Dum" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Var_A_Agregovany_Sklad" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Var_C_Hybrid" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Var_B_Polozkovy_Dum" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Var_B_Polozkovy_Sklad" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Var_D_PerPodlazi_Mistnost" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Var_E_Skladby_Vrstev" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Var_F_URS_Verification_Trail" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Souhrn" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Var_A_Agregovany_Dum" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Var_A_Agregovany_Sklad" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Var_C_Hybrid" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Var_B_Polozkovy_Dum" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Var_B_Polozkovy_Sklad" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Var_D_PerPodlazi_Mistnost" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Var_E_Skladby_Vrstev" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Var_F_URS_Verification_Trail" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Var_A_Agregovany_Dum'!$A$1:$G$17</definedName>
@@ -1085,7 +1085,7 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>8 WebSearch verified (3.7 %) ✓ | 5 wrong leaf flagged (2.3 %) ⚠ | 142 needs_production_lookup (66.4 %)</t>
+          <t>8 WebSearch verified (3.7 %) ✓ | 5 wrong leaf flagged (2.3 %) ⚠ | 141 needs_production_lookup (65.9 %)</t>
         </is>
       </c>
     </row>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>Terasa garapa — podkladní rošt — Terasa za opěrnou stěnou: rektifikovatelné terče 50 mm + betonové dlaždice 50 mm + štěrkový podsyp 16/32 mm tl. 100 mm + hrubý podsyp 4/8 mm tl. 150 mm + geotextilie</t>
+          <t>Terasa — podkladní skladba (pod dřevěnou pochozí vrstvou PSV76.002) — Terasa za opěrnou stěnou — PODKLADNÍ SKLADBA pod dřevěnou pochozí vrstvou (PSV76.002 Truhlář): rektifikovatelné terče výšky ~50 mm + betonové dlaždice tl. 50 mm jako roznášecí vrstva POD terče + štěrkový podsyp 16/32 mm tl. 100 mm + hrubý podsyp 4/8 mm tl. 150 mm + geotextilie separační</t>
         </is>
       </c>
       <c r="E6" s="20" t="inlineStr">
@@ -2226,7 +2226,7 @@
       </c>
       <c r="J6" s="8" t="inlineStr">
         <is>
-          <t>URS-prop 636311??? ?</t>
+          <t>URS-prop 564??? ?</t>
         </is>
       </c>
     </row>
@@ -6055,7 +6055,7 @@
         </is>
       </c>
       <c r="F102" s="22" t="n">
-        <v>6</v>
+        <v>0.6</v>
       </c>
       <c r="G102" s="10" t="n"/>
       <c r="H102" s="10" t="n"/>
@@ -7042,17 +7042,17 @@
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>Terasa garapa — podkladní rošt</t>
+          <t>Terasa — podkladní skladba (pod dřevěnou pochozí vrstvou PSV76.002)</t>
         </is>
       </c>
       <c r="D6" s="27" t="inlineStr">
         <is>
-          <t>636311??? ?</t>
+          <t>564??? ?</t>
         </is>
       </c>
       <c r="E6" s="8" t="inlineStr">
         <is>
-          <t>Terasa za opěrnou stěnou: rektifikovatelné terče 50 mm + betonové dlaždice 50 mm + štěrkový podsyp 16/32 mm tl. 100 mm + hrubý podsyp 4/8 mm tl. 150 mm + geotextilie</t>
+          <t>Terasa za opěrnou stěnou — PODKLADNÍ SKLADBA pod dřevěnou pochozí vrstvou (PSV76.002 Truhlář): rektifikovatelné terče výšky ~50 mm + betonové dlaždice tl. 50 mm jako roznášecí vrstva POD terče + štěrkový podsyp 16/32 mm tl. 100 mm + hrubý podsyp 4/8 mm tl. 150 mm + geotextilie separační</t>
         </is>
       </c>
       <c r="F6" s="20" t="inlineStr">
@@ -7075,12 +7075,12 @@
       </c>
       <c r="L6" s="20" t="inlineStr">
         <is>
-          <t>family_636311_leaf_lookup_required</t>
+          <t>family_564_leaf_lookup_required</t>
         </is>
       </c>
       <c r="M6" s="8" t="inlineStr">
         <is>
-          <t>PDF řez D.1.1.2.2.21 řez C-C explicit composition — 5-vrstvý podkladní systém terasa (Path C Tier 3 embedded tables); dřevěná prkna garapa same item v PSV-76 Truhlář</t>
+          <t>PDF řez D.1.1.2.2.21 řez C-C explicit composition — podkladní skladba terasy (terče + dlaždice roznášecí + podsypy + geotextilie); dřevěná pochozí vrstva (prkna garapa + dřevěný rošt) = samostatná položka PSV76.002 Truhlář (split-by-trade)</t>
         </is>
       </c>
       <c r="N6" s="20" t="inlineStr">
@@ -11470,7 +11470,7 @@
         </is>
       </c>
       <c r="G76" s="22" t="n">
-        <v>6</v>
+        <v>0.6</v>
       </c>
       <c r="H76" s="10" t="n"/>
       <c r="I76" s="10" t="n"/>
@@ -12585,17 +12585,17 @@
       </c>
       <c r="C94" s="8" t="inlineStr">
         <is>
-          <t>Terasa garapa za opěrnou stěnou</t>
-        </is>
-      </c>
-      <c r="D94" s="20" t="inlineStr">
-        <is>
-          <t>771474112</t>
+          <t>Terasa garapa za opěrnou stěnou — dřevěná pochozí vrstva</t>
+        </is>
+      </c>
+      <c r="D94" s="27" t="inlineStr">
+        <is>
+          <t>762??? ?</t>
         </is>
       </c>
       <c r="E94" s="8" t="inlineStr">
         <is>
-          <t>Dřevěná terasa za opěrnou stěnou — prkna garapa 145×25 mm na hliníkový rošt na rektifikovatelných terčích</t>
+          <t>Dřevěná terasa za opěrnou stěnou — prkna garapa 145×25 mm na dřevěném roštu z hranolů 50 mm na rektifikovatelných terčích (terče + podkladní skladba viz HSV1.005)</t>
         </is>
       </c>
       <c r="F94" s="20" t="inlineStr">
@@ -12618,12 +12618,12 @@
       </c>
       <c r="L94" s="20" t="inlineStr">
         <is>
-          <t>needs_production_lookup</t>
+          <t>family_762_leaf_lookup_required</t>
         </is>
       </c>
       <c r="M94" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 + DXF dum_situace PLOT_DREVENY_04 (terasa, ne 3.NP)</t>
+          <t>TZ ARS dům §4 + DXF dum_situace PLOT_DREVENY_04 (terasa, ne 3.NP); ŘEZ C-C potvrzuje dřevěný rošt z hranolů (NE hliníkový) + dřevěnou pochozí vrstvu</t>
         </is>
       </c>
       <c r="N94" s="20" t="inlineStr">

--- a/test-data/RD_Jachymov_dum/outputs/Vykaz_vymer_RD_Jachymov_VSE_VARIANTY_2026-05-29.xlsx
+++ b/test-data/RD_Jachymov_dum/outputs/Vykaz_vymer_RD_Jachymov_VSE_VARIANTY_2026-05-29.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Souhrn" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Var_A_Agregovany_Dum" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Var_A_Agregovany_Sklad" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Var_C_Hybrid" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Var_B_Polozkovy_Dum" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Var_B_Polozkovy_Sklad" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Var_D_PerPodlazi_Mistnost" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Var_E_Skladby_Vrstev" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Var_F_URS_Verification_Trail" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Souhrn" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Var_A_Agregovany_Dum" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Var_A_Agregovany_Sklad" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Var_C_Hybrid" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Var_B_Polozkovy_Dum" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Var_B_Polozkovy_Sklad" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Var_D_PerPodlazi_Mistnost" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Var_E_Skladby_Vrstev" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Var_F_URS_Verification_Trail" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Var_A_Agregovany_Dum'!$A$1:$G$17</definedName>

--- a/test-data/RD_Jachymov_dum/outputs/Vykaz_vymer_RD_Jachymov_VSE_VARIANTY_2026-05-29.xlsx
+++ b/test-data/RD_Jachymov_dum/outputs/Vykaz_vymer_RD_Jachymov_VSE_VARIANTY_2026-05-29.xlsx
@@ -1085,7 +1085,7 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>8 WebSearch verified (3.7 %) ✓ | 5 wrong leaf flagged (2.3 %) ⚠ | 142 needs_production_lookup (66.4 %)</t>
+          <t>8 WebSearch verified (3.7 %) ✓ | 5 wrong leaf flagged (2.3 %) ⚠ | 141 needs_production_lookup (65.9 %)</t>
         </is>
       </c>
     </row>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>Terasa garapa — podkladní rošt — Terasa za opěrnou stěnou: rektifikovatelné terče 50 mm + betonové dlaždice 50 mm + štěrkový podsyp 16/32 mm tl. 100 mm + hrubý podsyp 4/8 mm tl. 150 mm + geotextilie</t>
+          <t>Terasa — podkladní skladba (pod dřevěnou pochozí vrstvou PSV76.002) — Terasa za opěrnou stěnou — PODKLADNÍ SKLADBA pod dřevěnou pochozí vrstvou (PSV76.002 Truhlář): rektifikovatelné terče výšky ~50 mm + betonové dlaždice tl. 50 mm jako roznášecí vrstva POD terče + štěrkový podsyp 16/32 mm tl. 100 mm + hrubý podsyp 4/8 mm tl. 150 mm + geotextilie separační</t>
         </is>
       </c>
       <c r="E6" s="20" t="inlineStr">
@@ -2226,7 +2226,7 @@
       </c>
       <c r="J6" s="8" t="inlineStr">
         <is>
-          <t>URS-prop 636311??? ?</t>
+          <t>URS-prop 564??? ?</t>
         </is>
       </c>
     </row>
@@ -6055,7 +6055,7 @@
         </is>
       </c>
       <c r="F102" s="22" t="n">
-        <v>6</v>
+        <v>0.6</v>
       </c>
       <c r="G102" s="10" t="n"/>
       <c r="H102" s="10" t="n"/>
@@ -7042,17 +7042,17 @@
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>Terasa garapa — podkladní rošt</t>
+          <t>Terasa — podkladní skladba (pod dřevěnou pochozí vrstvou PSV76.002)</t>
         </is>
       </c>
       <c r="D6" s="27" t="inlineStr">
         <is>
-          <t>636311??? ?</t>
+          <t>564??? ?</t>
         </is>
       </c>
       <c r="E6" s="8" t="inlineStr">
         <is>
-          <t>Terasa za opěrnou stěnou: rektifikovatelné terče 50 mm + betonové dlaždice 50 mm + štěrkový podsyp 16/32 mm tl. 100 mm + hrubý podsyp 4/8 mm tl. 150 mm + geotextilie</t>
+          <t>Terasa za opěrnou stěnou — PODKLADNÍ SKLADBA pod dřevěnou pochozí vrstvou (PSV76.002 Truhlář): rektifikovatelné terče výšky ~50 mm + betonové dlaždice tl. 50 mm jako roznášecí vrstva POD terče + štěrkový podsyp 16/32 mm tl. 100 mm + hrubý podsyp 4/8 mm tl. 150 mm + geotextilie separační</t>
         </is>
       </c>
       <c r="F6" s="20" t="inlineStr">
@@ -7075,12 +7075,12 @@
       </c>
       <c r="L6" s="20" t="inlineStr">
         <is>
-          <t>family_636311_leaf_lookup_required</t>
+          <t>family_564_leaf_lookup_required</t>
         </is>
       </c>
       <c r="M6" s="8" t="inlineStr">
         <is>
-          <t>PDF řez D.1.1.2.2.21 řez C-C explicit composition — 5-vrstvý podkladní systém terasa (Path C Tier 3 embedded tables); dřevěná prkna garapa same item v PSV-76 Truhlář</t>
+          <t>PDF řez D.1.1.2.2.21 řez C-C explicit composition — podkladní skladba terasy (terče + dlaždice roznášecí + podsypy + geotextilie); dřevěná pochozí vrstva (prkna garapa + dřevěný rošt) = samostatná položka PSV76.002 Truhlář (split-by-trade)</t>
         </is>
       </c>
       <c r="N6" s="20" t="inlineStr">
@@ -11470,7 +11470,7 @@
         </is>
       </c>
       <c r="G76" s="22" t="n">
-        <v>6</v>
+        <v>0.6</v>
       </c>
       <c r="H76" s="10" t="n"/>
       <c r="I76" s="10" t="n"/>
@@ -12585,17 +12585,17 @@
       </c>
       <c r="C94" s="8" t="inlineStr">
         <is>
-          <t>Terasa garapa za opěrnou stěnou</t>
-        </is>
-      </c>
-      <c r="D94" s="20" t="inlineStr">
-        <is>
-          <t>771474112</t>
+          <t>Terasa garapa za opěrnou stěnou — dřevěná pochozí vrstva</t>
+        </is>
+      </c>
+      <c r="D94" s="27" t="inlineStr">
+        <is>
+          <t>762??? ?</t>
         </is>
       </c>
       <c r="E94" s="8" t="inlineStr">
         <is>
-          <t>Dřevěná terasa za opěrnou stěnou — prkna garapa 145×25 mm na hliníkový rošt na rektifikovatelných terčích</t>
+          <t>Dřevěná terasa za opěrnou stěnou — prkna garapa 145×25 mm na dřevěném roštu z hranolů 50 mm na rektifikovatelných terčích (terče + podkladní skladba viz HSV1.005)</t>
         </is>
       </c>
       <c r="F94" s="20" t="inlineStr">
@@ -12618,12 +12618,12 @@
       </c>
       <c r="L94" s="20" t="inlineStr">
         <is>
-          <t>needs_production_lookup</t>
+          <t>family_762_leaf_lookup_required</t>
         </is>
       </c>
       <c r="M94" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 + DXF dum_situace PLOT_DREVENY_04 (terasa, ne 3.NP)</t>
+          <t>TZ ARS dům §4 + DXF dum_situace PLOT_DREVENY_04 (terasa, ne 3.NP); ŘEZ C-C potvrzuje dřevěný rošt z hranolů (NE hliníkový) + dřevěnou pochozí vrstvu</t>
         </is>
       </c>
       <c r="N94" s="20" t="inlineStr">
